--- a/demo/4_売上_合計つき.xlsx
+++ b/demo/4_売上_合計つき.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -46,8 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,16 +417,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>商品</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>件数</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>単価</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>売上</t>
         </is>
@@ -435,7 +449,14 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1200</v>
+        <v>12</v>
+      </c>
+      <c r="C2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D2">
+        <f>B2*C2</f>
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -445,7 +466,14 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>800</v>
+        <v>8</v>
+      </c>
+      <c r="C3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3">
+        <f>B3*C3</f>
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -455,17 +483,42 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1500</v>
+        <v>5</v>
+      </c>
+      <c r="C4" t="n">
+        <v>300</v>
+      </c>
+      <c r="D4">
+        <f>B4*C4</f>
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C5" t="n">
+        <v>60</v>
+      </c>
+      <c r="D5">
+        <f>B5*C5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>3500</v>
+      <c r="D6">
+        <f>SUM(D2:D5)</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/demo/4_売上_合計つき.xlsx
+++ b/demo/4_売上_合計つき.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="売上" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="売上表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
